--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_COUGAR.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_COUGAR.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -573,10 +574,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -630,7 +636,8 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:L4"/>
